--- a/figures/fig2b_mock/fig2bc_rawdata.xlsx
+++ b/figures/fig2b_mock/fig2bc_rawdata.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>n = 1.9 + 0.02i, fixed at 50 nm</t>
+          <t>n = 1.8636 + 0.0032285i at 550 nm — Koenig et al., ACS Nano 8, 6182 (2014); identical to the l_ITO entry of the project library.  Fixed at 50 nm</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>nsub_al.csv and nsub_ag.csv (model output), fig2b_curves.csv (the assembled curves)</t>
+          <t>nsub_al_konig.csv and nsub_ag_konig.csv (model output), fig2b_curves_konig.csv (the assembled curves).  The earlier n = 1.9 + 0.02i run is kept alongside as nsub_{al,ag}.csv / fig2b_curves.csv</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>column 9 of nsub_al.csv and nsub_ag.csv is eta_ext at the script's default p = 0.4 and is NOT the plotted curve; the workbook recomputes eta_ext from the p column</t>
+          <t>column 9 of nsub_al_konig.csv and nsub_ag_konig.csv is eta_ext at the script's default p = 0.4 and is NOT the plotted curve; the workbook recomputes eta_ext from the p column</t>
         </is>
       </c>
     </row>
@@ -870,10 +870,10 @@
         <v>0.665</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0.2545774488953764</v>
+        <v>0.2643436524424712</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.1659048386562776</v>
+        <v>0.127513651056066</v>
       </c>
       <c r="E5" s="6">
         <f>$B5/($B5+(1-$B5)*D5)</f>
@@ -884,10 +884,10 @@
         <v/>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.3024157950855146</v>
+        <v>0.3102576096370601</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.06793277330241843</v>
+        <v>0.02467922944151324</v>
       </c>
       <c r="I5" s="6">
         <f>$B5/($B5+(1-$B5)*H5)</f>
@@ -913,10 +913,10 @@
         <v>0.5674999999999998</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0.2739293239366931</v>
+        <v>0.2846069769589232</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.1657270360038535</v>
+        <v>0.1285904009083063</v>
       </c>
       <c r="E6" s="6">
         <f>$B6/($B6+(1-$B6)*D6)</f>
@@ -927,10 +927,10 @@
         <v/>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.318976400432224</v>
+        <v>0.3232301328544434</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.06579309378438669</v>
+        <v>0.02423035724052003</v>
       </c>
       <c r="I6" s="6">
         <f>$B6/($B6+(1-$B6)*H6)</f>
@@ -956,10 +956,10 @@
         <v>0.47</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.3037928927091349</v>
+        <v>0.3167121480835495</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.1697294850183797</v>
+        <v>0.1334600546963324</v>
       </c>
       <c r="E7" s="6">
         <f>$B7/($B7+(1-$B7)*D7)</f>
@@ -970,10 +970,10 @@
         <v/>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.3415836846459211</v>
+        <v>0.3493549601261782</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.06474222095509419</v>
+        <v>0.0242200900544588</v>
       </c>
       <c r="I7" s="6">
         <f>$B7/($B7+(1-$B7)*H7)</f>
@@ -999,10 +999,10 @@
         <v>0.425</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>0.3551349980120916</v>
+        <v>0.3718099523933531</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.1811984239350622</v>
+        <v>0.144087229442619</v>
       </c>
       <c r="E8" s="6">
         <f>$B8/($B8+(1-$B8)*D8)</f>
@@ -1013,10 +1013,10 @@
         <v/>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.3802224941362572</v>
+        <v>0.393044740502608</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.06627047452721235</v>
+        <v>0.02525198681334395</v>
       </c>
       <c r="I8" s="6">
         <f>$B8/($B8+(1-$B8)*H8)</f>
@@ -1042,10 +1042,10 @@
         <v>0.38</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.3844789689500101</v>
+        <v>0.3971364906508024</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.1810440950425944</v>
+        <v>0.1425860031475392</v>
       </c>
       <c r="E9" s="6">
         <f>$B9/($B9+(1-$B9)*D9)</f>
@@ -1056,10 +1056,10 @@
         <v/>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.4548819218007782</v>
+        <v>0.4648878933082227</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.07248190902324114</v>
+        <v>0.02761053763287613</v>
       </c>
       <c r="I9" s="6">
         <f>$B9/($B9+(1-$B9)*H9)</f>
@@ -1085,10 +1085,10 @@
         <v>0.3675</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>0.4117535494246413</v>
+        <v>0.4254052938799134</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.179203536958368</v>
+        <v>0.1402645134132884</v>
       </c>
       <c r="E10" s="6">
         <f>$B10/($B10+(1-$B10)*D10)</f>
@@ -1099,10 +1099,10 @@
         <v/>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.4831441894132887</v>
+        <v>0.4965449423869523</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.07200156338461183</v>
+        <v>0.02700309134341428</v>
       </c>
       <c r="I10" s="6">
         <f>$B10/($B10+(1-$B10)*H10)</f>
@@ -1128,10 +1128,10 @@
         <v>0.355</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>0.4907922493568424</v>
+        <v>0.5426338462761358</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0.1874601489333053</v>
+        <v>0.1446627347371449</v>
       </c>
       <c r="E11" s="6">
         <f>$B11/($B11+(1-$B11)*D11)</f>
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.5426903154356646</v>
+        <v>0.5961745973282631</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.07741128204254277</v>
+        <v>0.02862634701144451</v>
       </c>
       <c r="I11" s="6">
         <f>$B11/($B11+(1-$B11)*H11)</f>
@@ -1171,10 +1171,10 @@
         <v>0.345</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>0.576772213350746</v>
+        <v>0.5953914122155134</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0.1892409705954347</v>
+        <v>0.1419769693230359</v>
       </c>
       <c r="E12" s="6">
         <f>$B12/($B12+(1-$B12)*D12)</f>
@@ -1185,10 +1185,10 @@
         <v/>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.6449751942229809</v>
+        <v>0.6700142925330348</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.08229988694412904</v>
+        <v>0.02848420353442793</v>
       </c>
       <c r="I12" s="6">
         <f>$B12/($B12+(1-$B12)*H12)</f>
@@ -1214,10 +1214,10 @@
         <v>0.335</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>0.6313366791406457</v>
+        <v>0.6463252042063352</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0.1852333418677616</v>
+        <v>0.1403940097162457</v>
       </c>
       <c r="E13" s="6">
         <f>$B13/($B13+(1-$B13)*D13)</f>
@@ -1228,10 +1228,10 @@
         <v/>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.7037447197003757</v>
+        <v>0.7152268381342591</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.07794869666057691</v>
+        <v>0.02726715260983725</v>
       </c>
       <c r="I13" s="6">
         <f>$B13/($B13+(1-$B13)*H13)</f>
@@ -1257,10 +1257,10 @@
         <v>0.32</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>0.7045822180273082</v>
+        <v>0.7272278417955491</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>0.1888162703045277</v>
+        <v>0.1448159499572754</v>
       </c>
       <c r="E14" s="6">
         <f>$B14/($B14+(1-$B14)*D14)</f>
@@ -1271,10 +1271,10 @@
         <v/>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.7882315817034957</v>
+        <v>0.8091242106824427</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.07711381756291869</v>
+        <v>0.02714463189577498</v>
       </c>
       <c r="I14" s="6">
         <f>$B14/($B14+(1-$B14)*H14)</f>
@@ -1300,10 +1300,10 @@
         <v>0.305</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>0.7977863715925674</v>
+        <v>0.8417932956443259</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.2063895661447593</v>
+        <v>0.149691844732431</v>
       </c>
       <c r="E15" s="6">
         <f>$B15/($B15+(1-$B15)*D15)</f>
@@ -1314,10 +1314,10 @@
         <v/>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.906372492901554</v>
+        <v>0.9564053370395643</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.09484795756961406</v>
+        <v>0.03101144029276803</v>
       </c>
       <c r="I15" s="6">
         <f>$B15/($B15+(1-$B15)*H15)</f>
@@ -1343,10 +1343,10 @@
         <v>0.29</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>0.8138885356680825</v>
+        <v>0.8446524578282923</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0.2071701428266887</v>
+        <v>0.1458192855974815</v>
       </c>
       <c r="E16" s="6">
         <f>$B16/($B16+(1-$B16)*D16)</f>
@@ -1357,10 +1357,10 @@
         <v/>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.9231840071516172</v>
+        <v>0.9581165835015284</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.09769004561430816</v>
+        <v>0.02980749399405036</v>
       </c>
       <c r="I16" s="6">
         <f>$B16/($B16+(1-$B16)*H16)</f>
@@ -1386,10 +1386,10 @@
         <v>0.275</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.8224174261689127</v>
+        <v>0.8496464096317363</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0.2041217389818678</v>
+        <v>0.1429699104615599</v>
       </c>
       <c r="E17" s="6">
         <f>$B17/($B17+(1-$B17)*D17)</f>
@@ -1400,10 +1400,10 @@
         <v/>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.9270369085304827</v>
+        <v>0.9585272683290416</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.09527246431063385</v>
+        <v>0.02857666161312056</v>
       </c>
       <c r="I17" s="6">
         <f>$B17/($B17+(1-$B17)*H17)</f>
@@ -1429,10 +1429,10 @@
         <v>0.2615</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>0.825345393955061</v>
+        <v>0.8509849593837161</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>0.1958626295442895</v>
+        <v>0.135962854140796</v>
       </c>
       <c r="E18" s="6">
         <f>$B18/($B18+(1-$B18)*D18)</f>
@@ -1443,10 +1443,10 @@
         <v/>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.9291546156250079</v>
+        <v>0.9588130841108791</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.09243339670071671</v>
+        <v>0.02741875995814513</v>
       </c>
       <c r="I18" s="6">
         <f>$B18/($B18+(1-$B18)*H18)</f>
@@ -1472,10 +1472,10 @@
         <v>0.248</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.8265366790000138</v>
+        <v>0.8511194700177727</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0.1875901535665955</v>
+        <v>0.1291310523745816</v>
       </c>
       <c r="E19" s="6">
         <f>$B19/($B19+(1-$B19)*D19)</f>
@@ -1486,10 +1486,10 @@
         <v/>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.9305851916225563</v>
+        <v>0.9590369961667355</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.08956914925587744</v>
+        <v>0.02633755973635477</v>
       </c>
       <c r="I19" s="6">
         <f>$B19/($B19+(1-$B19)*H19)</f>
@@ -1604,28 +1604,28 @@
         <v>1.3</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.2545774488953764</v>
+        <v>0.2643436524424712</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0.6332986276155114</v>
+        <v>0.6314549124732671</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.08547101963826516</v>
+        <v>0.08443368721221765</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>0.02665290385084564</v>
+        <v>0.0197677478720459</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.01814047192867344</v>
+        <v>0.01834648276869922</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.008512431922172194</v>
+        <v>0.001421265103346674</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.1659048386562776</v>
+        <v>0.127513651056066</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.8007320241017315</v>
+        <v>0.8394399254042152</v>
       </c>
       <c r="J5" s="6">
         <f>B5+C5+D5+E5</f>
@@ -1637,28 +1637,28 @@
         <v>1.35</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.2739293239366931</v>
+        <v>0.2846069769589232</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0.6110365691341281</v>
+        <v>0.6084478618170807</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.0853891383349899</v>
+        <v>0.08441670612170357</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>0.02964496859418707</v>
+        <v>0.02252845510229628</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.02072985750015078</v>
+        <v>0.02103525789285884</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.008915111094036289</v>
+        <v>0.001493197209437435</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.1657270360038535</v>
+        <v>0.1285904009083063</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.800903063691903</v>
+        <v>0.8383033535301673</v>
       </c>
       <c r="J6" s="6">
         <f>B6+C6+D6+E6</f>
@@ -1670,28 +1670,28 @@
         <v>1.4</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.3037928927091349</v>
+        <v>0.3167121480835495</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.5753028178983235</v>
+        <v>0.5710661495692642</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.08533355228149984</v>
+        <v>0.0842981461951154</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>0.0355707371110425</v>
+        <v>0.02792355615207419</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.02541829733835217</v>
+        <v>0.02619577381779789</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.01015243977269033</v>
+        <v>0.001727782334276296</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.1697294850183797</v>
+        <v>0.1334600546963324</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.7970704615552882</v>
+        <v>0.8332013528194809</v>
       </c>
       <c r="J7" s="6">
         <f>B7+C7+D7+E7</f>
@@ -1703,28 +1703,28 @@
         <v>1.45</v>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.3551349980120916</v>
+        <v>0.3718099523933531</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>0.5100590716554946</v>
+        <v>0.5042255886889814</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.08532763204309457</v>
+        <v>0.08428159257185963</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>0.04947829828931629</v>
+        <v>0.03968286634581038</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.0358858673709734</v>
+        <v>0.03732876677877972</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.01359243091834289</v>
+        <v>0.002354099567030664</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.1811984239350622</v>
+        <v>0.144087229442619</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.7862886136679292</v>
+        <v>0.8222799419971005</v>
       </c>
       <c r="J8" s="6">
         <f>B8+C8+D8+E8</f>
@@ -1736,28 +1736,28 @@
         <v>1.5</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.3844789689500101</v>
+        <v>0.3971364906508024</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.4797044034704833</v>
+        <v>0.4796738151947358</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.08534082907014726</v>
+        <v>0.08425332218106102</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0.05047579850935856</v>
+        <v>0.03893637197340265</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.03659373905628695</v>
+        <v>0.03661623425014537</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.01388205945307161</v>
+        <v>0.002320137723257271</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.1810440950425944</v>
+        <v>0.1425860031475392</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.7864317604302316</v>
+        <v>0.8238053348896889</v>
       </c>
       <c r="J9" s="6">
         <f>B9+C9+D9+E9</f>
@@ -1769,28 +1769,28 @@
         <v>1.55</v>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.4117535494246413</v>
+        <v>0.4254052938799134</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>0.4490831355544669</v>
+        <v>0.4493123051988074</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.0854166219629118</v>
+        <v>0.08419063524184134</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>0.0537466930579802</v>
+        <v>0.04109176567944298</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.03835399403940289</v>
+        <v>0.03847148082686728</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.0153926990185773</v>
+        <v>0.002620284852575705</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.179203536958368</v>
+        <v>0.1402645134132884</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.7881429843605096</v>
+        <v>0.8261753704951763</v>
       </c>
       <c r="J10" s="6">
         <f>B10+C10+D10+E10</f>
@@ -1802,28 +1802,28 @@
         <v>1.6</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.4907922493568424</v>
+        <v>0.5426338462761358</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>0.3483000097989973</v>
+        <v>0.315940280203726</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0.08553445979704365</v>
+        <v>0.08439485272290392</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>0.07537328104711459</v>
+        <v>0.05703102079723674</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0.04590444193411538</v>
+        <v>0.05008993128154125</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.02946883911299922</v>
+        <v>0.006941089515695486</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.1874601489333053</v>
+        <v>0.1446627347371449</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.7805242201632248</v>
+        <v>0.8216966690879924</v>
       </c>
       <c r="J11" s="6">
         <f>B11+C11+D11+E11</f>
@@ -1835,28 +1835,28 @@
         <v>1.65</v>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0.576772213350746</v>
+        <v>0.5953914122155134</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>0.2600744015379385</v>
+        <v>0.2700978650532886</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0.08583879475660366</v>
+        <v>0.08444523613818736</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>0.07731459035471498</v>
+        <v>0.05006548659301378</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.04595986943045505</v>
+        <v>0.04496373460357959</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.03135472092425993</v>
+        <v>0.00510175198943419</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.1892409705954347</v>
+        <v>0.1419769693230359</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.7789002430206331</v>
+        <v>0.8244257878202804</v>
       </c>
       <c r="J12" s="6">
         <f>B12+C12+D12+E12</f>
@@ -1868,28 +1868,28 @@
         <v>1.7</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0.6313366791406457</v>
+        <v>0.6463252042063352</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>0.2038066838905713</v>
+        <v>0.2177994534013124</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0.08629652341230211</v>
+        <v>0.08463006631155388</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>0.07856011355647928</v>
+        <v>0.05124527608079703</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0.04724860755944332</v>
+        <v>0.04612469553203106</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.03131150599703597</v>
+        <v>0.005120580548765971</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.1852333418677616</v>
+        <v>0.1403940097162457</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.782564455907884</v>
+        <v>0.826042807158609</v>
       </c>
       <c r="J13" s="6">
         <f>B13+C13+D13+E13</f>
@@ -1901,28 +1901,28 @@
         <v>1.75</v>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0.7045822180273082</v>
+        <v>0.7272278417955491</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>0.1210531099856355</v>
+        <v>0.1303717636107894</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>0.08721770323213403</v>
+        <v>0.08501650441312299</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>0.08714696875492532</v>
+        <v>0.05738389018054128</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.05204628013601804</v>
+        <v>0.05137138238673982</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.03510068861890728</v>
+        <v>0.00601250779380146</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.1888162703045277</v>
+        <v>0.1448159499572754</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.7792869242102891</v>
+        <v>0.8215415253628456</v>
       </c>
       <c r="J14" s="6">
         <f>B14+C14+D14+E14</f>
@@ -1934,28 +1934,28 @@
         <v>1.8</v>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0.7977863715925674</v>
+        <v>0.8417932956443259</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.09616488378217412</v>
+        <v>0.08661956947989839</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>0.106048744625259</v>
+        <v>0.07158713487577675</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.06355517951703957</v>
+        <v>0.06382390364646624</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.04249356510821947</v>
+        <v>0.007763231229310507</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.2063895661447593</v>
+        <v>0.149691844732431</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.7636010621215757</v>
+        <v>0.8166346738078532</v>
       </c>
       <c r="J15" s="6">
         <f>B15+C15+D15+E15</f>
@@ -1967,28 +1967,28 @@
         <v>1.85</v>
       </c>
       <c r="B16" s="6" t="n">
-        <v>0.8138885356680825</v>
+        <v>0.8446524578282923</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0.06101955143734605</v>
+        <v>0.05958384481442479</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>0.1250919128945714</v>
+        <v>0.09576369735728378</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.08802284608650267</v>
+        <v>0.0888010458774157</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.03706906680806872</v>
+        <v>0.00696265147986808</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.2071701428266887</v>
+        <v>0.1458192855974815</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.7629189562902431</v>
+        <v>0.8205270070317794</v>
       </c>
       <c r="J16" s="6">
         <f>B16+C16+D16+E16</f>
@@ -2000,28 +2000,28 @@
         <v>1.9</v>
       </c>
       <c r="B17" s="6" t="n">
-        <v>0.8224174261689127</v>
+        <v>0.8496464096317363</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0.008548044949204334</v>
+        <v>0.008136927146930865</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>0.1690345288818833</v>
+        <v>0.1422166632213345</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0.1336581940482593</v>
+        <v>0.1349450755989534</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.035376334833624</v>
+        <v>0.007271587622381122</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.2041217389818678</v>
+        <v>0.1429699104615599</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.7655897372337604</v>
+        <v>0.8234147091418809</v>
       </c>
       <c r="J17" s="6">
         <f>B17+C17+D17+E17</f>
@@ -2033,28 +2033,28 @@
         <v>1.95</v>
       </c>
       <c r="B18" s="6" t="n">
-        <v>0.825345393955061</v>
+        <v>0.8509849593837161</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>0.002203462931598873</v>
+        <v>0.002076403566429343</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>0.1724511431133393</v>
+        <v>0.146938637049857</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.1388853140641125</v>
+        <v>0.1397759348993622</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.03356582904922682</v>
+        <v>0.007162702150494852</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.1958626295442895</v>
+        <v>0.135962854140796</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.772920606401773</v>
+        <v>0.8306032227620853</v>
       </c>
       <c r="J18" s="6">
         <f>B18+C18+D18+E18</f>
@@ -2066,28 +2066,28 @@
         <v>2</v>
       </c>
       <c r="B19" s="6" t="n">
-        <v>0.8265366790000138</v>
+        <v>0.8511194700177727</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0.0009107429419475065</v>
+        <v>0.0008514810023383668</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.1725525780580406</v>
+        <v>0.14802904897989</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0.1403857069703003</v>
+        <v>0.1410760225217151</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.03216687108774027</v>
+        <v>0.006953026458174911</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.1875901535665955</v>
+        <v>0.1291310523745816</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.7804054364876217</v>
+        <v>0.8377338244571063</v>
       </c>
       <c r="J19" s="6">
         <f>B19+C19+D19+E19</f>
@@ -2191,28 +2191,28 @@
         <v>1.3</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.3024157950855146</v>
+        <v>0.3102576096370601</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0.6561704376829135</v>
+        <v>0.6580385864976068</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.02850308519284721</v>
+        <v>0.02759856321485092</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>0.01291068203872528</v>
+        <v>0.004105240650476019</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.002368269464151806</v>
+        <v>0.00236684983219697</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.01054241257457347</v>
+        <v>0.001738390818279048</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.06793277330241843</v>
+        <v>0.02467922944151324</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.9075240605883429</v>
+        <v>0.9643026311713991</v>
       </c>
       <c r="J5" s="6">
         <f>B5+C5+D5+E5</f>
@@ -2224,28 +2224,28 @@
         <v>1.35</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.318976400432224</v>
+        <v>0.3232301328544434</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0.6394233552263976</v>
+        <v>0.6452699133067714</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.02843003884697655</v>
+        <v>0.02720357897294941</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>0.01317020549440188</v>
+        <v>0.004296374865832865</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.002604227478874283</v>
+        <v>0.002573658095399578</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.01056597801552759</v>
+        <v>0.001722716770433286</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.06579309378438669</v>
+        <v>0.02423035724052003</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.9101751422578206</v>
+        <v>0.9649291335726248</v>
       </c>
       <c r="J6" s="6">
         <f>B6+C6+D6+E6</f>
@@ -2257,28 +2257,28 @@
         <v>1.4</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.3415836846459211</v>
+        <v>0.3493549601261782</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.6159626554355735</v>
+        <v>0.6184807287029964</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.02836702256351838</v>
+        <v>0.02735037522123212</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>0.0140866373549892</v>
+        <v>0.00481393594959295</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.00297314596303004</v>
+        <v>0.002978057417042646</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.01111349139195916</v>
+        <v>0.001835878532550305</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.06474222095509419</v>
+        <v>0.0242200900544588</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.9114828626630324</v>
+        <v>0.9649434732699108</v>
       </c>
       <c r="J7" s="6">
         <f>B7+C7+D7+E7</f>
@@ -2290,28 +2290,28 @@
         <v>1.45</v>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.3802224941362572</v>
+        <v>0.393044740502608</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>0.5747390611858434</v>
+        <v>0.5735486783749905</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.02831694462127933</v>
+        <v>0.02734640756801534</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>0.01672150005662205</v>
+        <v>0.006060173554384184</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.003721551048912977</v>
+        <v>0.003842185065028818</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.01299994900770907</v>
+        <v>0.002217988489355365</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.06627047452721235</v>
+        <v>0.02525198681334395</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.9095823218628755</v>
+        <v>0.9635043994169852</v>
       </c>
       <c r="J8" s="6">
         <f>B8+C8+D8+E8</f>
@@ -2323,28 +2323,28 @@
         <v>1.5</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.4548819218007782</v>
+        <v>0.4648878933082227</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.4924695085614986</v>
+        <v>0.4995259285180944</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.02828412656922709</v>
+        <v>0.02701467056776351</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0.02436444306849718</v>
+        <v>0.008571507605919897</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.005511024482866022</v>
+        <v>0.005444888343472837</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.01885341858563115</v>
+        <v>0.003126619262447059</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.07248190902324114</v>
+        <v>0.02761053763287613</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.9019386475099572</v>
+        <v>0.9602312484669111</v>
       </c>
       <c r="J9" s="6">
         <f>B9+C9+D9+E9</f>
@@ -2356,28 +2356,28 @@
         <v>1.55</v>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.4831441894132887</v>
+        <v>0.4965449423869523</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>0.4651079919321005</v>
+        <v>0.4679035692882099</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.02827069121864925</v>
+        <v>0.02737023414436076</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>0.02347712743596005</v>
+        <v>0.008181254180475602</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.005145796569672563</v>
+        <v>0.005113058478493612</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.01833133086628748</v>
+        <v>0.00306819570198199</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.07200156338461183</v>
+        <v>0.02700309134341428</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.9025251656219011</v>
+        <v>0.9610721225315089</v>
       </c>
       <c r="J10" s="6">
         <f>B10+C10+D10+E10</f>
@@ -2389,28 +2389,28 @@
         <v>1.6</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.5426903154356646</v>
+        <v>0.5961745973282631</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>0.3968655759734769</v>
+        <v>0.3636521155259948</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0.02829061997024972</v>
+        <v>0.02791839864363277</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>0.03215348862060101</v>
+        <v>0.01225488850210913</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0.005598507484126235</v>
+        <v>0.006135649123794648</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.02655498113647478</v>
+        <v>0.006119239378314478</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.07741128204254277</v>
+        <v>0.02862634701144451</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.8959634777823585</v>
+        <v>0.9588283695531318</v>
       </c>
       <c r="J11" s="6">
         <f>B11+C11+D11+E11</f>
@@ -2422,28 +2422,28 @@
         <v>1.65</v>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0.6449751942229809</v>
+        <v>0.6700142925330348</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>0.2865559567445752</v>
+        <v>0.2911237550152911</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0.02836971078470408</v>
+        <v>0.027563911786152</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>0.04009913824773126</v>
+        <v>0.01129804066551866</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.005753205922402837</v>
+        <v>0.005668445892139809</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.03434593232532842</v>
+        <v>0.005629594773378847</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.08229988694412904</v>
+        <v>0.02848420353442793</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.8901154042896066</v>
+        <v>0.9590244294361769</v>
       </c>
       <c r="J12" s="6">
         <f>B12+C12+D12+E12</f>
@@ -2455,28 +2455,28 @@
         <v>1.7</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0.7037447197003757</v>
+        <v>0.7152268381342591</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>0.2278895461368492</v>
+        <v>0.2465215852498305</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0.02855716153170796</v>
+        <v>0.02715586020543369</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>0.03980857263106145</v>
+        <v>0.0110957164104803</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0.005725174958551839</v>
+        <v>0.005556270213726216</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.03408339767250961</v>
+        <v>0.005539446196754089</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.07794869666057691</v>
+        <v>0.02726715260983725</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.8953168300043253</v>
+        <v>0.9607064076538797</v>
       </c>
       <c r="J13" s="6">
         <f>B13+C13+D13+E13</f>
@@ -2488,28 +2488,28 @@
         <v>1.75</v>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0.7882315817034957</v>
+        <v>0.8091242106824427</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>0.1380432336624733</v>
+        <v>0.1512402417797345</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>0.0290743251927819</v>
+        <v>0.02718971949528728</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>0.04465085944125431</v>
+        <v>0.01244582804253206</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.006011784766547671</v>
+        <v>0.005868638878799601</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.03863907467470663</v>
+        <v>0.006577189163732457</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.07711381756291869</v>
+        <v>0.02714463189577498</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.8963218056967522</v>
+        <v>0.9608760595971585</v>
       </c>
       <c r="J14" s="6">
         <f>B14+C14+D14+E14</f>
@@ -2521,28 +2521,28 @@
         <v>1.8</v>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0.906372492901554</v>
+        <v>0.9564053370395643</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.03797141737522846</v>
+        <v>0.02784576845559609</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>0.05565608972321385</v>
+        <v>0.01574889450483933</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.006789511388776328</v>
+        <v>0.006804316135852907</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.04886657833443752</v>
+        <v>0.008944578368986421</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.09484795756961406</v>
+        <v>0.03101144029276803</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.8754482782720862</v>
+        <v>0.9555505039022657</v>
       </c>
       <c r="J15" s="6">
         <f>B15+C15+D15+E15</f>
@@ -2554,28 +2554,28 @@
         <v>1.85</v>
       </c>
       <c r="B16" s="6" t="n">
-        <v>0.9231840071516172</v>
+        <v>0.9581165835015284</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0.02738999985823456</v>
+        <v>0.02662281634464115</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>0.04942599299014548</v>
+        <v>0.01526060015382982</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.007287573592019093</v>
+        <v>0.007273978824189831</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.04213841939812639</v>
+        <v>0.007986621329639993</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.09769004561430816</v>
+        <v>0.02980749399405036</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.8721931212943969</v>
+        <v>0.9572022974035775</v>
       </c>
       <c r="J16" s="6">
         <f>B16+C16+D16+E16</f>
@@ -2587,28 +2587,28 @@
         <v>1.9</v>
       </c>
       <c r="B17" s="6" t="n">
-        <v>0.9270369085304827</v>
+        <v>0.9585272683290416</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0.02641290991159205</v>
+        <v>0.02611696197604132</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>0.04655018155793249</v>
+        <v>0.01535576969491302</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0.007746225253528874</v>
+        <v>0.007733074680361618</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.03880395630440361</v>
+        <v>0.0076226950145514</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.09527246431063385</v>
+        <v>0.02857666161312056</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.8749605310486774</v>
+        <v>0.9588968919934454</v>
       </c>
       <c r="J17" s="6">
         <f>B17+C17+D17+E17</f>
@@ -2620,28 +2620,28 @@
         <v>1.95</v>
       </c>
       <c r="B18" s="6" t="n">
-        <v>0.9291546156250079</v>
+        <v>0.9588130841108791</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>0.02572311222206426</v>
+        <v>0.02555196886512523</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>0.0451222721529282</v>
+        <v>0.0156349470239949</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.00831928505572071</v>
+        <v>0.008310248148102287</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.03680298709720749</v>
+        <v>0.007324698875892613</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.09243339670071671</v>
+        <v>0.02741875995814513</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.878232921901389</v>
+        <v>0.9604965629497847</v>
       </c>
       <c r="J18" s="6">
         <f>B18+C18+D18+E18</f>
@@ -2653,28 +2653,28 @@
         <v>2</v>
       </c>
       <c r="B19" s="6" t="n">
-        <v>0.9305851916225563</v>
+        <v>0.9590369961667355</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0.02452012737264999</v>
+        <v>0.02439478667026792</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.04489468100479317</v>
+        <v>0.01656821716299562</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0.009500621753608884</v>
+        <v>0.009494633781076178</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.03539405925118429</v>
+        <v>0.007073583381919443</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.08956914925587744</v>
+        <v>0.02633755973635477</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.8815592340775203</v>
+        <v>0.9619950950760321</v>
       </c>
       <c r="J19" s="6">
         <f>B19+C19+D19+E19</f>

--- a/figures/fig2b_mock/fig2bc_rawdata.xlsx
+++ b/figures/fig2b_mock/fig2bc_rawdata.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -639,120 +639,132 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>extraction loss</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>eta_sub - EQE: what reached the substrate and never escaped.  This is the shaded band of panel (c).  FORMULA</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
           <t>p (flat interface)</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>reference column only, not used by any formula: the escape probability of a flat substrate/air interface for angularly randomised light, mean Fresnel transmittance over the escape cone divided by n_sub^2 (Yablonovitch 1982, one-sided)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Sheets</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>fig2b_2c</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>the plotted curves, with eta_ext and EQE as formulas</t>
+          <t>Sheets</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Al_modes</t>
+          <t>fig2b_2c</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>the full five-channel power budget for the Al reflector, as the model returns it</t>
+          <t>the plotted curves, with eta_ext and EQE as formulas</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>Al_modes</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>the full five-channel power budget for the Al reflector, as the model returns it</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
           <t>Ag_modes</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>the same for the Ag reflector</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Provenance</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Script</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>sim/design_rule4/dr4f.m (Octave), MODE=nsub, run with UNUM=3000 and TOPMAT=al / ag</t>
+          <t>Provenance</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Source files</t>
+          <t>Script</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>nsub_al_konig.csv and nsub_ag_konig.csv (model output), fig2b_curves_konig.csv (the assembled curves).  The earlier n = 1.9 + 0.02i run is kept alongside as nsub_{al,ag}.csv / fig2b_curves.csv</t>
+          <t>sim/design_rule4/dr4f.m (Octave), MODE=nsub, run with UNUM=3000 and TOPMAT=al / ag</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>Source files</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>interpolated from the author's single-pass escape-probability curve: 0.665 / 0.470 / 0.380 / 0.355 / 0.335 / 0.305 / 0.275 / 0.248 at n_sub = 1.30 / 1.40 / 1.50 / 1.60 / 1.70 / 1.80 / 1.90 / 2.00</t>
+          <t>nsub_al_konig.csv and nsub_ag_konig.csv (model output), fig2b_curves_konig.csv (the assembled curves).  The earlier n = 1.9 + 0.02i run is kept alongside as nsub_{al,ag}.csv / fig2b_curves.csv</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Caution</t>
+          <t>p</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>column 9 of nsub_al_konig.csv and nsub_ag_konig.csv is eta_ext at the script's default p = 0.4 and is NOT the plotted curve; the workbook recomputes eta_ext from the p column</t>
+          <t>interpolated from the author's single-pass escape-probability curve: 0.665 / 0.470 / 0.380 / 0.355 / 0.335 / 0.305 / 0.275 / 0.248 at n_sub = 1.30 / 1.40 / 1.50 / 1.60 / 1.70 / 1.80 / 1.90 / 2.00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>Caution</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>column 9 of nsub_al_konig.csv and nsub_ag_konig.csv is eta_ext at the script's default p = 0.4 and is NOT the plotted curve; the workbook recomputes eta_ext from the p column</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
           <t>Repository</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>jjoono/OLED-, branch claude/oled-efficiency-paper-ag-955zsk, figures/fig2b_mock/</t>
         </is>
@@ -769,7 +781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -784,6 +796,8 @@
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -796,7 +810,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>eta_ext = p/[p+(1-p)A'] and EQE = eta_sub x eta_ext are formulas; edit column B (yellow) to redraw with a different p</t>
+          <t>eta_ext, EQE and the two loss columns are formulas; edit column B (yellow) to redraw everything with a different p</t>
         </is>
       </c>
     </row>
@@ -857,6 +871,16 @@
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>extraction loss (Al)</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>extraction loss (Ag)</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>p, flat interface (reference)</t>
         </is>
@@ -901,7 +925,15 @@
         <f>I5-E5</f>
         <v/>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="L5" s="6">
+        <f>C5-F5</f>
+        <v/>
+      </c>
+      <c r="M5" s="6">
+        <f>G5-J5</f>
+        <v/>
+      </c>
+      <c r="N5" s="6" t="n">
         <v>0.5555426141807783</v>
       </c>
     </row>
@@ -944,7 +976,15 @@
         <f>I6-E6</f>
         <v/>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="L6" s="6">
+        <f>C6-F6</f>
+        <v/>
+      </c>
+      <c r="M6" s="6">
+        <f>G6-J6</f>
+        <v/>
+      </c>
+      <c r="N6" s="6" t="n">
         <v>0.5107915418560387</v>
       </c>
     </row>
@@ -987,7 +1027,15 @@
         <f>I7-E7</f>
         <v/>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="L7" s="6">
+        <f>C7-F7</f>
+        <v/>
+      </c>
+      <c r="M7" s="6">
+        <f>G7-J7</f>
+        <v/>
+      </c>
+      <c r="N7" s="6" t="n">
         <v>0.4710139087909155</v>
       </c>
     </row>
@@ -1030,7 +1078,15 @@
         <f>I8-E8</f>
         <v/>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="L8" s="6">
+        <f>C8-F8</f>
+        <v/>
+      </c>
+      <c r="M8" s="6">
+        <f>G8-J8</f>
+        <v/>
+      </c>
+      <c r="N8" s="6" t="n">
         <v>0.4354967086478286</v>
       </c>
     </row>
@@ -1073,7 +1129,15 @@
         <f>I9-E9</f>
         <v/>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="L9" s="6">
+        <f>C9-F9</f>
+        <v/>
+      </c>
+      <c r="M9" s="6">
+        <f>G9-J9</f>
+        <v/>
+      </c>
+      <c r="N9" s="6" t="n">
         <v>0.4036536942292964</v>
       </c>
     </row>
@@ -1116,7 +1180,15 @@
         <f>I10-E10</f>
         <v/>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="L10" s="6">
+        <f>C10-F10</f>
+        <v/>
+      </c>
+      <c r="M10" s="6">
+        <f>G10-J10</f>
+        <v/>
+      </c>
+      <c r="N10" s="6" t="n">
         <v>0.374998094679025</v>
       </c>
     </row>
@@ -1159,7 +1231,15 @@
         <f>I11-E11</f>
         <v/>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="L11" s="6">
+        <f>C11-F11</f>
+        <v/>
+      </c>
+      <c r="M11" s="6">
+        <f>G11-J11</f>
+        <v/>
+      </c>
+      <c r="N11" s="6" t="n">
         <v>0.3491223309818853</v>
       </c>
     </row>
@@ -1202,7 +1282,15 @@
         <f>I12-E12</f>
         <v/>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="L12" s="6">
+        <f>C12-F12</f>
+        <v/>
+      </c>
+      <c r="M12" s="6">
+        <f>G12-J12</f>
+        <v/>
+      </c>
+      <c r="N12" s="6" t="n">
         <v>0.3256826182327374</v>
       </c>
     </row>
@@ -1245,7 +1333,15 @@
         <f>I13-E13</f>
         <v/>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="L13" s="6">
+        <f>C13-F13</f>
+        <v/>
+      </c>
+      <c r="M13" s="6">
+        <f>G13-J13</f>
+        <v/>
+      </c>
+      <c r="N13" s="6" t="n">
         <v>0.3043870816108616</v>
       </c>
     </row>
@@ -1288,7 +1384,15 @@
         <f>I14-E14</f>
         <v/>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="L14" s="6">
+        <f>C14-F14</f>
+        <v/>
+      </c>
+      <c r="M14" s="6">
+        <f>G14-J14</f>
+        <v/>
+      </c>
+      <c r="N14" s="6" t="n">
         <v>0.284986457384909</v>
       </c>
     </row>
@@ -1331,7 +1435,15 @@
         <f>I15-E15</f>
         <v/>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="L15" s="6">
+        <f>C15-F15</f>
+        <v/>
+      </c>
+      <c r="M15" s="6">
+        <f>G15-J15</f>
+        <v/>
+      </c>
+      <c r="N15" s="6" t="n">
         <v>0.2672667313252264</v>
       </c>
     </row>
@@ -1374,7 +1486,15 @@
         <f>I16-E16</f>
         <v/>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="L16" s="6">
+        <f>C16-F16</f>
+        <v/>
+      </c>
+      <c r="M16" s="6">
+        <f>G16-J16</f>
+        <v/>
+      </c>
+      <c r="N16" s="6" t="n">
         <v>0.2510432517074033</v>
       </c>
     </row>
@@ -1417,7 +1537,15 @@
         <f>I17-E17</f>
         <v/>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="L17" s="6">
+        <f>C17-F17</f>
+        <v/>
+      </c>
+      <c r="M17" s="6">
+        <f>G17-J17</f>
+        <v/>
+      </c>
+      <c r="N17" s="6" t="n">
         <v>0.236155979456892</v>
       </c>
     </row>
@@ -1460,7 +1588,15 @@
         <f>I18-E18</f>
         <v/>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="L18" s="6">
+        <f>C18-F18</f>
+        <v/>
+      </c>
+      <c r="M18" s="6">
+        <f>G18-J18</f>
+        <v/>
+      </c>
+      <c r="N18" s="6" t="n">
         <v>0.2224656252191622</v>
       </c>
     </row>
@@ -1503,7 +1639,15 @@
         <f>I19-E19</f>
         <v/>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="L19" s="6">
+        <f>C19-F19</f>
+        <v/>
+      </c>
+      <c r="M19" s="6">
+        <f>G19-J19</f>
+        <v/>
+      </c>
+      <c r="N19" s="6" t="n">
         <v>0.2098504851395527</v>
       </c>
     </row>
